--- a/01_Input/00_CO Validation/Honduras - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Honduras - Energy Projects.xlsx
@@ -975,7 +975,7 @@
       <c r="X5" s="3" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="12">
+  <dataValidations count="10">
     <dataValidation sqref="Q2:Q4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
     </dataValidation>
@@ -1002,12 +1002,6 @@
     </dataValidation>
     <dataValidation sqref="R2:R4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Electricity Access, Energy Efficiency, Renewable Energy, Infrastructure,  Transport, Digital &amp; Data, Clean Cooking, Decarbonization, Hydrogen, Off-Grid, On-Grid, Research &amp; Innovation, Grant &amp; Investment"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
     </dataValidation>
     <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
       <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
